--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742583</v>
+        <v>122742590</v>
       </c>
       <c r="B2" t="n">
-        <v>57384</v>
+        <v>90958</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739429</v>
+        <v>739327</v>
       </c>
       <c r="R2" t="n">
-        <v>7148907</v>
+        <v>7148896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742587</v>
+        <v>122742586</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739280</v>
+        <v>739277</v>
       </c>
       <c r="R3" t="n">
-        <v>7148886</v>
+        <v>7148880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742593</v>
+        <v>122742592</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>90905</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739263</v>
+        <v>739314</v>
       </c>
       <c r="R4" t="n">
-        <v>7148897</v>
+        <v>7148917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742586</v>
+        <v>122742580</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,14 +1029,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739277</v>
+        <v>739311</v>
       </c>
       <c r="R5" t="n">
-        <v>7148880</v>
+        <v>7148969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742584</v>
+        <v>122742585</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739271</v>
+        <v>739267</v>
       </c>
       <c r="R6" t="n">
-        <v>7148843</v>
+        <v>7148864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742585</v>
+        <v>122742587</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739267</v>
+        <v>739280</v>
       </c>
       <c r="R7" t="n">
-        <v>7148864</v>
+        <v>7148886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742590</v>
+        <v>122742593</v>
       </c>
       <c r="B8" t="n">
-        <v>90855</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739327</v>
+        <v>739263</v>
       </c>
       <c r="R8" t="n">
-        <v>7148896</v>
+        <v>7148897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742592</v>
+        <v>122742583</v>
       </c>
       <c r="B9" t="n">
-        <v>90802</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,38 +1429,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739314</v>
+        <v>739429</v>
       </c>
       <c r="R9" t="n">
-        <v>7148917</v>
+        <v>7148907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1530,7 +1530,7 @@
         <v>122742589</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>122742588</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742580</v>
+        <v>122742584</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,14 +1775,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739311</v>
+        <v>739271</v>
       </c>
       <c r="R12" t="n">
-        <v>7148969</v>
+        <v>7148843</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742590</v>
+        <v>122742586</v>
       </c>
       <c r="B2" t="n">
-        <v>90958</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739327</v>
+        <v>739277</v>
       </c>
       <c r="R2" t="n">
-        <v>7148896</v>
+        <v>7148880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742586</v>
+        <v>122742580</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739277</v>
+        <v>739311</v>
       </c>
       <c r="R3" t="n">
-        <v>7148880</v>
+        <v>7148969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742592</v>
+        <v>122742593</v>
       </c>
       <c r="B4" t="n">
-        <v>90905</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739314</v>
+        <v>739263</v>
       </c>
       <c r="R4" t="n">
-        <v>7148917</v>
+        <v>7148897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742580</v>
+        <v>122742592</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739311</v>
+        <v>739314</v>
       </c>
       <c r="R5" t="n">
-        <v>7148969</v>
+        <v>7148917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742585</v>
+        <v>122742584</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739267</v>
+        <v>739271</v>
       </c>
       <c r="R6" t="n">
-        <v>7148864</v>
+        <v>7148843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742587</v>
+        <v>122742590</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>90962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1217,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739280</v>
+        <v>739327</v>
       </c>
       <c r="R7" t="n">
-        <v>7148886</v>
+        <v>7148896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742593</v>
+        <v>122742583</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739263</v>
+        <v>739429</v>
       </c>
       <c r="R8" t="n">
-        <v>7148897</v>
+        <v>7148907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742583</v>
+        <v>122742589</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,42 +1433,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739429</v>
+        <v>739332</v>
       </c>
       <c r="R9" t="n">
-        <v>7148907</v>
+        <v>7148898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742589</v>
+        <v>122742587</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739332</v>
+        <v>739280</v>
       </c>
       <c r="R10" t="n">
-        <v>7148898</v>
+        <v>7148886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1636,7 @@
         <v>122742588</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742584</v>
+        <v>122742585</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,14 +1775,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739271</v>
+        <v>739267</v>
       </c>
       <c r="R12" t="n">
-        <v>7148843</v>
+        <v>7148864</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742590</v>
+        <v>122742583</v>
       </c>
       <c r="B7" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739327</v>
+        <v>739429</v>
       </c>
       <c r="R7" t="n">
-        <v>7148896</v>
+        <v>7148907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742583</v>
+        <v>122742590</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,38 +1331,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739429</v>
+        <v>739327</v>
       </c>
       <c r="R8" t="n">
-        <v>7148907</v>
+        <v>7148896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742587</v>
+        <v>122742588</v>
       </c>
       <c r="B10" t="n">
         <v>98355</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739280</v>
+        <v>739286</v>
       </c>
       <c r="R10" t="n">
-        <v>7148886</v>
+        <v>7148882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742588</v>
+        <v>122742587</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739286</v>
+        <v>739280</v>
       </c>
       <c r="R11" t="n">
-        <v>7148882</v>
+        <v>7148886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742586</v>
+        <v>122742580</v>
       </c>
       <c r="B2" t="n">
         <v>98355</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739277</v>
+        <v>739311</v>
       </c>
       <c r="R2" t="n">
-        <v>7148880</v>
+        <v>7148969</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742580</v>
+        <v>122742585</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739311</v>
+        <v>739267</v>
       </c>
       <c r="R3" t="n">
-        <v>7148969</v>
+        <v>7148864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742593</v>
+        <v>122742592</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739263</v>
+        <v>739314</v>
       </c>
       <c r="R4" t="n">
-        <v>7148897</v>
+        <v>7148917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742592</v>
+        <v>122742590</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739314</v>
+        <v>739327</v>
       </c>
       <c r="R5" t="n">
-        <v>7148917</v>
+        <v>7148896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742584</v>
+        <v>122742593</v>
       </c>
       <c r="B6" t="n">
         <v>98355</v>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739271</v>
+        <v>739263</v>
       </c>
       <c r="R6" t="n">
-        <v>7148843</v>
+        <v>7148897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742583</v>
+        <v>122742587</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739429</v>
+        <v>739280</v>
       </c>
       <c r="R7" t="n">
-        <v>7148907</v>
+        <v>7148886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742590</v>
+        <v>122742584</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739327</v>
+        <v>739271</v>
       </c>
       <c r="R8" t="n">
-        <v>7148896</v>
+        <v>7148843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1527,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742588</v>
+        <v>122742583</v>
       </c>
       <c r="B10" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1535,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739286</v>
+        <v>739429</v>
       </c>
       <c r="R10" t="n">
-        <v>7148882</v>
+        <v>7148907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,7 +1633,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742587</v>
+        <v>122742586</v>
       </c>
       <c r="B11" t="n">
         <v>98355</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739280</v>
+        <v>739277</v>
       </c>
       <c r="R11" t="n">
-        <v>7148886</v>
+        <v>7148880</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742585</v>
+        <v>122742588</v>
       </c>
       <c r="B12" t="n">
         <v>98355</v>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739267</v>
+        <v>739286</v>
       </c>
       <c r="R12" t="n">
-        <v>7148864</v>
+        <v>7148882</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122742580</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742585</v>
+        <v>122742588</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739267</v>
+        <v>739286</v>
       </c>
       <c r="R3" t="n">
-        <v>7148864</v>
+        <v>7148882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742592</v>
+        <v>122742583</v>
       </c>
       <c r="B4" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739314</v>
+        <v>739429</v>
       </c>
       <c r="R4" t="n">
-        <v>7148917</v>
+        <v>7148907</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742590</v>
+        <v>122742585</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739327</v>
+        <v>739267</v>
       </c>
       <c r="R5" t="n">
-        <v>7148896</v>
+        <v>7148864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742593</v>
+        <v>122742589</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739263</v>
+        <v>739332</v>
       </c>
       <c r="R6" t="n">
-        <v>7148897</v>
+        <v>7148898</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1212,7 @@
         <v>122742587</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742584</v>
+        <v>122742586</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,14 +1351,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739271</v>
+        <v>739277</v>
       </c>
       <c r="R8" t="n">
-        <v>7148843</v>
+        <v>7148880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742589</v>
+        <v>122742593</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1457,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739332</v>
+        <v>739263</v>
       </c>
       <c r="R9" t="n">
-        <v>7148898</v>
+        <v>7148897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742583</v>
+        <v>122742584</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,42 +1539,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739429</v>
+        <v>739271</v>
       </c>
       <c r="R10" t="n">
-        <v>7148907</v>
+        <v>7148843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742586</v>
+        <v>122742590</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>90962</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739277</v>
+        <v>739327</v>
       </c>
       <c r="R11" t="n">
-        <v>7148880</v>
+        <v>7148896</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742588</v>
+        <v>122742592</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,25 +1751,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739286</v>
+        <v>739314</v>
       </c>
       <c r="R12" t="n">
-        <v>7148882</v>
+        <v>7148917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742580</v>
+        <v>122742590</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739311</v>
+        <v>739327</v>
       </c>
       <c r="R2" t="n">
-        <v>7148969</v>
+        <v>7148896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742588</v>
+        <v>122742589</v>
       </c>
       <c r="B3" t="n">
         <v>98357</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739286</v>
+        <v>739332</v>
       </c>
       <c r="R3" t="n">
-        <v>7148882</v>
+        <v>7148898</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742583</v>
+        <v>122742593</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,42 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739429</v>
+        <v>739263</v>
       </c>
       <c r="R4" t="n">
-        <v>7148907</v>
+        <v>7148897</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -997,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742585</v>
+        <v>122742588</v>
       </c>
       <c r="B5" t="n">
         <v>98357</v>
@@ -1037,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739267</v>
+        <v>739286</v>
       </c>
       <c r="R5" t="n">
-        <v>7148864</v>
+        <v>7148882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742589</v>
+        <v>122742586</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1143,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739332</v>
+        <v>739277</v>
       </c>
       <c r="R6" t="n">
-        <v>7148898</v>
+        <v>7148880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742587</v>
+        <v>122742583</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,38 +1217,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739280</v>
+        <v>739429</v>
       </c>
       <c r="R7" t="n">
-        <v>7148886</v>
+        <v>7148907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>90909</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R8" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742593</v>
+        <v>122742585</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1461,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739263</v>
+        <v>739267</v>
       </c>
       <c r="R9" t="n">
-        <v>7148897</v>
+        <v>7148864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742590</v>
+        <v>122742587</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739327</v>
+        <v>739280</v>
       </c>
       <c r="R11" t="n">
-        <v>7148896</v>
+        <v>7148886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742592</v>
+        <v>122742580</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>98357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,38 +1751,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739314</v>
+        <v>739311</v>
       </c>
       <c r="R12" t="n">
-        <v>7148917</v>
+        <v>7148969</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742583</v>
+        <v>122742585</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739429</v>
+        <v>739267</v>
       </c>
       <c r="R7" t="n">
-        <v>7148907</v>
+        <v>7148864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742585</v>
+        <v>122742583</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,38 +1429,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739267</v>
+        <v>739429</v>
       </c>
       <c r="R9" t="n">
-        <v>7148864</v>
+        <v>7148907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742585</v>
+        <v>122742583</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739267</v>
+        <v>739429</v>
       </c>
       <c r="R7" t="n">
-        <v>7148864</v>
+        <v>7148907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742583</v>
+        <v>122742585</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,42 +1433,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739429</v>
+        <v>739267</v>
       </c>
       <c r="R9" t="n">
-        <v>7148907</v>
+        <v>7148864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742590</v>
+        <v>122742587</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739327</v>
+        <v>739280</v>
       </c>
       <c r="R2" t="n">
-        <v>7148896</v>
+        <v>7148886</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742589</v>
+        <v>122742580</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739332</v>
+        <v>739311</v>
       </c>
       <c r="R3" t="n">
-        <v>7148898</v>
+        <v>7148969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742593</v>
+        <v>122742586</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739263</v>
+        <v>739277</v>
       </c>
       <c r="R4" t="n">
-        <v>7148897</v>
+        <v>7148880</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742588</v>
+        <v>122742589</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739286</v>
+        <v>739332</v>
       </c>
       <c r="R5" t="n">
-        <v>7148882</v>
+        <v>7148898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742586</v>
+        <v>122742584</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,14 +1135,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739277</v>
+        <v>739271</v>
       </c>
       <c r="R6" t="n">
-        <v>7148880</v>
+        <v>7148843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742583</v>
+        <v>122742590</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,38 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739429</v>
+        <v>739327</v>
       </c>
       <c r="R7" t="n">
-        <v>7148907</v>
+        <v>7148896</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742592</v>
+        <v>122742585</v>
       </c>
       <c r="B8" t="n">
-        <v>90909</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739314</v>
+        <v>739267</v>
       </c>
       <c r="R8" t="n">
-        <v>7148917</v>
+        <v>7148864</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742585</v>
+        <v>122742583</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,38 +1429,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739267</v>
+        <v>739429</v>
       </c>
       <c r="R9" t="n">
-        <v>7148864</v>
+        <v>7148907</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742584</v>
+        <v>122742588</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,14 +1563,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739271</v>
+        <v>739286</v>
       </c>
       <c r="R10" t="n">
-        <v>7148843</v>
+        <v>7148882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742587</v>
+        <v>122742592</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739280</v>
+        <v>739314</v>
       </c>
       <c r="R11" t="n">
-        <v>7148886</v>
+        <v>7148917</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742580</v>
+        <v>122742593</v>
       </c>
       <c r="B12" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,14 +1775,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739311</v>
+        <v>739263</v>
       </c>
       <c r="R12" t="n">
-        <v>7148969</v>
+        <v>7148897</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742586</v>
+        <v>122742589</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739277</v>
+        <v>739332</v>
       </c>
       <c r="R4" t="n">
-        <v>7148880</v>
+        <v>7148898</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742589</v>
+        <v>122742586</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739332</v>
+        <v>739277</v>
       </c>
       <c r="R5" t="n">
-        <v>7148898</v>
+        <v>7148880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742587</v>
+        <v>122742585</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739280</v>
+        <v>739267</v>
       </c>
       <c r="R2" t="n">
-        <v>7148886</v>
+        <v>7148864</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742580</v>
+        <v>122742593</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739311</v>
+        <v>739263</v>
       </c>
       <c r="R3" t="n">
-        <v>7148969</v>
+        <v>7148897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742589</v>
+        <v>122742588</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739332</v>
+        <v>739286</v>
       </c>
       <c r="R4" t="n">
-        <v>7148898</v>
+        <v>7148882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742586</v>
+        <v>122742587</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739277</v>
+        <v>739280</v>
       </c>
       <c r="R5" t="n">
-        <v>7148880</v>
+        <v>7148886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742584</v>
+        <v>122742583</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739271</v>
+        <v>739429</v>
       </c>
       <c r="R6" t="n">
-        <v>7148843</v>
+        <v>7148907</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1311,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742585</v>
+        <v>122742584</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1347,14 +1351,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739267</v>
+        <v>739271</v>
       </c>
       <c r="R8" t="n">
-        <v>7148864</v>
+        <v>7148843</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742583</v>
+        <v>122742580</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,42 +1433,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739429</v>
+        <v>739311</v>
       </c>
       <c r="R9" t="n">
-        <v>7148907</v>
+        <v>7148969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742588</v>
+        <v>122742589</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739286</v>
+        <v>739332</v>
       </c>
       <c r="R10" t="n">
-        <v>7148882</v>
+        <v>7148898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742592</v>
+        <v>122742586</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739314</v>
+        <v>739277</v>
       </c>
       <c r="R11" t="n">
-        <v>7148917</v>
+        <v>7148880</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742593</v>
+        <v>122742592</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,25 +1751,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739263</v>
+        <v>739314</v>
       </c>
       <c r="R12" t="n">
-        <v>7148897</v>
+        <v>7148917</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R11" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742592</v>
+        <v>122742586</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,25 +1751,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739314</v>
+        <v>739277</v>
       </c>
       <c r="R12" t="n">
-        <v>7148917</v>
+        <v>7148880</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742585</v>
+        <v>122742584</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739267</v>
+        <v>739271</v>
       </c>
       <c r="R2" t="n">
-        <v>7148864</v>
+        <v>7148843</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742593</v>
+        <v>122742583</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739263</v>
+        <v>739429</v>
       </c>
       <c r="R3" t="n">
-        <v>7148897</v>
+        <v>7148907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742588</v>
+        <v>122742587</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739286</v>
+        <v>739280</v>
       </c>
       <c r="R4" t="n">
-        <v>7148882</v>
+        <v>7148886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742587</v>
+        <v>122742589</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1033,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739280</v>
+        <v>739332</v>
       </c>
       <c r="R5" t="n">
-        <v>7148886</v>
+        <v>7148898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742583</v>
+        <v>122742586</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,42 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739429</v>
+        <v>739277</v>
       </c>
       <c r="R6" t="n">
-        <v>7148907</v>
+        <v>7148880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742590</v>
+        <v>122742580</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,38 +1221,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739327</v>
+        <v>739311</v>
       </c>
       <c r="R7" t="n">
-        <v>7148896</v>
+        <v>7148969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742584</v>
+        <v>122742588</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1351,14 +1351,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739271</v>
+        <v>739286</v>
       </c>
       <c r="R8" t="n">
-        <v>7148843</v>
+        <v>7148882</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742580</v>
+        <v>122742585</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1457,14 +1457,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739311</v>
+        <v>739267</v>
       </c>
       <c r="R9" t="n">
-        <v>7148969</v>
+        <v>7148864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742589</v>
+        <v>122742593</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739332</v>
+        <v>739263</v>
       </c>
       <c r="R10" t="n">
-        <v>7148898</v>
+        <v>7148897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742586</v>
+        <v>122742590</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,25 +1751,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739277</v>
+        <v>739327</v>
       </c>
       <c r="R12" t="n">
-        <v>7148880</v>
+        <v>7148896</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742584</v>
+        <v>122742593</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739271</v>
+        <v>739263</v>
       </c>
       <c r="R2" t="n">
-        <v>7148843</v>
+        <v>7148897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742583</v>
+        <v>122742587</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739429</v>
+        <v>739280</v>
       </c>
       <c r="R3" t="n">
-        <v>7148907</v>
+        <v>7148886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -891,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742587</v>
+        <v>122742584</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -927,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739280</v>
+        <v>739271</v>
       </c>
       <c r="R4" t="n">
-        <v>7148886</v>
+        <v>7148843</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +993,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742589</v>
+        <v>122742586</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1037,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739332</v>
+        <v>739277</v>
       </c>
       <c r="R5" t="n">
-        <v>7148898</v>
+        <v>7148880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R6" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742580</v>
+        <v>122742585</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1245,14 +1241,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739311</v>
+        <v>739267</v>
       </c>
       <c r="R7" t="n">
-        <v>7148969</v>
+        <v>7148864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742588</v>
+        <v>122742590</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739286</v>
+        <v>739327</v>
       </c>
       <c r="R8" t="n">
-        <v>7148882</v>
+        <v>7148896</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742585</v>
+        <v>122742580</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1457,14 +1453,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739267</v>
+        <v>739311</v>
       </c>
       <c r="R9" t="n">
-        <v>7148864</v>
+        <v>7148969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742593</v>
+        <v>122742583</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1535,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739263</v>
+        <v>739429</v>
       </c>
       <c r="R10" t="n">
-        <v>7148897</v>
+        <v>7148907</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742592</v>
+        <v>122742589</v>
       </c>
       <c r="B11" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,25 +1645,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739314</v>
+        <v>739332</v>
       </c>
       <c r="R11" t="n">
-        <v>7148917</v>
+        <v>7148898</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742590</v>
+        <v>122742588</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,25 +1751,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739327</v>
+        <v>739286</v>
       </c>
       <c r="R12" t="n">
-        <v>7148896</v>
+        <v>7148882</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R5" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742592</v>
+        <v>122742586</v>
       </c>
       <c r="B6" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739314</v>
+        <v>739277</v>
       </c>
       <c r="R6" t="n">
-        <v>7148917</v>
+        <v>7148880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742593</v>
+        <v>122742588</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739263</v>
+        <v>739286</v>
       </c>
       <c r="R2" t="n">
-        <v>7148897</v>
+        <v>7148882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742587</v>
+        <v>122742585</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739280</v>
+        <v>739267</v>
       </c>
       <c r="R3" t="n">
-        <v>7148886</v>
+        <v>7148864</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122742584</v>
+        <v>122742580</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,14 +923,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739271</v>
+        <v>739311</v>
       </c>
       <c r="R4" t="n">
-        <v>7148843</v>
+        <v>7148969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742592</v>
+        <v>122742590</v>
       </c>
       <c r="B5" t="n">
-        <v>90917</v>
+        <v>90973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739314</v>
+        <v>739327</v>
       </c>
       <c r="R5" t="n">
-        <v>7148917</v>
+        <v>7148896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>90920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R6" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742585</v>
+        <v>122742583</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,38 +1217,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739267</v>
+        <v>739429</v>
       </c>
       <c r="R7" t="n">
-        <v>7148864</v>
+        <v>7148907</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1311,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742590</v>
+        <v>122742586</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1327,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739327</v>
+        <v>739277</v>
       </c>
       <c r="R8" t="n">
-        <v>7148896</v>
+        <v>7148880</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742580</v>
+        <v>122742589</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,14 +1457,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739311</v>
+        <v>739332</v>
       </c>
       <c r="R9" t="n">
-        <v>7148969</v>
+        <v>7148898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742583</v>
+        <v>122742587</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,42 +1539,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739429</v>
+        <v>739280</v>
       </c>
       <c r="R10" t="n">
-        <v>7148907</v>
+        <v>7148886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1633,10 +1633,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742589</v>
+        <v>122742584</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,14 +1669,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739332</v>
+        <v>739271</v>
       </c>
       <c r="R11" t="n">
-        <v>7148898</v>
+        <v>7148843</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742588</v>
+        <v>122742593</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739286</v>
+        <v>739263</v>
       </c>
       <c r="R12" t="n">
-        <v>7148882</v>
+        <v>7148897</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122742588</v>
+        <v>122742590</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739286</v>
+        <v>739327</v>
       </c>
       <c r="R2" t="n">
-        <v>7148882</v>
+        <v>7148896</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122742585</v>
+        <v>122742584</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Finn-Olles- N, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>739267</v>
+        <v>739271</v>
       </c>
       <c r="R3" t="n">
-        <v>7148864</v>
+        <v>7148843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>122742580</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742590</v>
+        <v>122742592</v>
       </c>
       <c r="B5" t="n">
-        <v>90973</v>
+        <v>90922</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739327</v>
+        <v>739314</v>
       </c>
       <c r="R5" t="n">
-        <v>7148896</v>
+        <v>7148917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742592</v>
+        <v>122742586</v>
       </c>
       <c r="B6" t="n">
-        <v>90920</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739314</v>
+        <v>739277</v>
       </c>
       <c r="R6" t="n">
-        <v>7148917</v>
+        <v>7148880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122742583</v>
+        <v>122742588</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,42 +1217,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sörklubben NV, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>739429</v>
+        <v>739286</v>
       </c>
       <c r="R7" t="n">
-        <v>7148907</v>
+        <v>7148882</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1300,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kollberg</t>
+          <t>Helene Andersson, Elin Kollberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1315,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122742586</v>
+        <v>122742593</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>739277</v>
+        <v>739263</v>
       </c>
       <c r="R8" t="n">
-        <v>7148880</v>
+        <v>7148897</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122742589</v>
+        <v>122742587</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1461,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>739332</v>
+        <v>739280</v>
       </c>
       <c r="R9" t="n">
-        <v>7148898</v>
+        <v>7148886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122742587</v>
+        <v>122742585</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1567,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>739280</v>
+        <v>739267</v>
       </c>
       <c r="R10" t="n">
-        <v>7148886</v>
+        <v>7148864</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122742584</v>
+        <v>122742589</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,14 +1665,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finn-Olles- N, Vb</t>
+          <t>Rörtjärnarna NÖ, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>739271</v>
+        <v>739332</v>
       </c>
       <c r="R11" t="n">
-        <v>7148843</v>
+        <v>7148898</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1739,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122742593</v>
+        <v>122742583</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,38 +1747,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rörtjärnarna NÖ, Vb</t>
+          <t>Sörklubben NV, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>739263</v>
+        <v>739429</v>
       </c>
       <c r="R12" t="n">
-        <v>7148897</v>
+        <v>7148907</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helene Andersson, Elin Kollberg</t>
+          <t>Elin Kollberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 39942-2024 artfynd.xlsx
+++ b/artfynd/A 39942-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122742592</v>
+        <v>122742586</v>
       </c>
       <c r="B5" t="n">
-        <v>90922</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739314</v>
+        <v>739277</v>
       </c>
       <c r="R5" t="n">
-        <v>7148917</v>
+        <v>7148880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122742586</v>
+        <v>122742592</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>90922</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739277</v>
+        <v>739314</v>
       </c>
       <c r="R6" t="n">
-        <v>7148880</v>
+        <v>7148917</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
